--- a/CIS 4374 Homework 5.xlsx
+++ b/CIS 4374 Homework 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Stuff from D Drive\College Crap\Fall 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B42926E-0890-423D-B2A5-91CF84714021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA2443F-7060-44B3-8E78-E18A82246C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{FBC1D086-CDB1-4C4E-A8BD-698DF734EC27}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
   <si>
     <t xml:space="preserve">      </t>
   </si>
@@ -212,6 +212,18 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>Responsible</t>
+  </si>
+  <si>
+    <t>Accountable</t>
+  </si>
+  <si>
+    <t>Consulted</t>
+  </si>
+  <si>
+    <t>Informed</t>
   </si>
 </sst>
 </file>
@@ -239,7 +251,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -247,15 +259,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -972,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80FA9F17-174D-43DA-833D-28EEE438C7FF}">
-  <dimension ref="B2:H12"/>
+  <dimension ref="B2:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
@@ -1236,6 +1264,38 @@
         <v>54</v>
       </c>
     </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
